--- a/.schema/MHR_USER.xlsx
+++ b/.schema/MHR_USER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD4BF41B-6D15-4784-AC52-F88C27717B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CF743CA-B96A-43E8-A6B1-A9D3AC3D010D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5609E0F2-1DBE-4FF8-A7A2-727173935943}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{224A008E-9EFC-4953-824F-E6F8E8AA7524}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_USER" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+  <si>
+    <t>« NULL »</t>
+  </si>
   <si>
     <t>b109f3bbbc244eb82441917ed06d618b9008dd09b3befd1b5e07394c706a8bb980b1d7785e5976ec049b46df5f1326af5a2ea6d103fd07c95385ffab0cacbc86</t>
   </si>
@@ -46,12 +49,6 @@
     <t>hoge@example.com</t>
   </si>
   <si>
-    <t>管理者</t>
-  </si>
-  <si>
-    <t>システム</t>
-  </si>
-  <si>
     <t>UPDATE_USER_ID</t>
   </si>
   <si>
@@ -83,6 +80,76 @@
   </si>
   <si>
     <t>USER_ID</t>
+  </si>
+  <si>
+    <t>oracle/XEPDB1：emarf : 2026/03/05 17:37:44</t>
+  </si>
+  <si>
+    <t>権限</t>
+    <rPh sb="0" eb="2">
+      <t>ケンゲン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>参照</t>
+    <rPh sb="0" eb="2">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>検索</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出力</t>
+    <rPh sb="0" eb="2">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>追加</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>更新</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>削除</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>承認</t>
+    <rPh sb="0" eb="2">
+      <t>ショウニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>否認</t>
+    <rPh sb="0" eb="2">
+      <t>ヒニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -90,7 +157,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss.000"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -202,7 +269,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{377FEE4E-4679-41E9-B458-6285274125D8}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{59146721-A418-4020-BD89-0E00304E3880}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -513,8 +580,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F24DE5F-4D77-4449-87D8-B171384B941D}">
-  <dimension ref="A2:K3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35B18904-72EE-42F4-BD2B-BF09C4F5CAF5}">
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.5" style="1" bestFit="1" customWidth="1"/>
@@ -524,46 +591,51 @@
     <col min="5" max="5" width="29.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.59765625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
@@ -571,30 +643,318 @@
         <v>0</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="2">
+      <c r="F6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K11" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K3" xr:uid="{922026A8-5534-4074-BC0D-3E3696459C7A}"/>
+  <autoFilter ref="A2:K3" xr:uid="{2505A544-DBD0-4D11-AD4B-33F08D890A26}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
